--- a/backend/tmp/mda-package-archive/2026-06/SMPL_MDA_Package_2026-06.xlsx
+++ b/backend/tmp/mda-package-archive/2026-06/SMPL_MDA_Package_2026-06.xlsx
@@ -2008,21 +2008,6 @@
           <t>YTD Var %</t>
         </is>
       </c>
-      <c r="J4" s="58" t="inlineStr">
-        <is>
-          <t>Period vs Budget Commentary</t>
-        </is>
-      </c>
-      <c r="K4" s="58" t="inlineStr">
-        <is>
-          <t>QTD vs Budget Commentary</t>
-        </is>
-      </c>
-      <c r="L4" s="58" t="inlineStr">
-        <is>
-          <t>YTD vs Budget Commentary</t>
-        </is>
-      </c>
     </row>
     <row r="5" ht="16" customHeight="1" s="122">
       <c r="A5" s="59" t="inlineStr">
@@ -2551,28 +2536,28 @@
         </is>
       </c>
       <c r="B27" s="125" t="n">
-        <v>48.4318</v>
+        <v>30</v>
       </c>
       <c r="C27" s="125" t="n">
         <v>31.455591</v>
       </c>
       <c r="D27" s="128" t="n">
-        <v>16.976209</v>
+        <v>-1.455590999999998</v>
       </c>
       <c r="E27" s="129" t="n">
-        <v>0.5396881273030287</v>
+        <v>-0.04627447629262468</v>
       </c>
       <c r="F27" s="125" t="n">
-        <v>48.4318</v>
+        <v>30</v>
       </c>
       <c r="G27" s="125" t="n">
         <v>31.455591</v>
       </c>
       <c r="H27" s="128" t="n">
-        <v>16.976209</v>
+        <v>-1.455590999999998</v>
       </c>
       <c r="I27" s="129" t="n">
-        <v>0.5396881273030287</v>
+        <v>-0.04627447629262468</v>
       </c>
     </row>
   </sheetData>
@@ -3619,17 +3604,13 @@
       </c>
       <c r="AD6" s="150" t="inlineStr">
         <is>
-          <t>New Business ARR of $1.68M trailed budget $1.77M in June; the shortfall reflects timing of late-quarter closes and is the primary driver of the period Net New ARR miss of -$84.2K vs budget.</t>
-        </is>
-      </c>
-      <c r="AE6" s="150" t="inlineStr">
-        <is>
-          <t>Q2 New Business of $5.13M exceeded budget $5.08M by +$53.8K (+1.1%); the quarter-level result is favorable, confirming that earlier Q2 months overperformed and offset the June shortfall.</t>
-        </is>
-      </c>
+          <t>June New Business of $1.68M missed budget by $90.0K, -5.1% (sheets.arr_waterfall.arr_new_business.period.actual), indicating softer new logo acquisition.</t>
+        </is>
+      </c>
+      <c r="AE6" s="150" t="inlineStr"/>
       <c r="AF6" s="150" t="inlineStr">
         <is>
-          <t>YTD New Business of $9.18M vs budget $8.97M, +$215.8K (+2.4%) favorable; trend is improving through H1 and provides a constructive foundation for H2 quota attainment.</t>
+          <t>YTD New Business of $9.18M exceeds budget by $215.8K, +2.4% (sheets.arr_waterfall.arr_new_business.ytd.actual), demonstrating resilience in new customer wins despite June miss.</t>
         </is>
       </c>
     </row>
@@ -3725,17 +3706,17 @@
       </c>
       <c r="AD7" s="150" t="inlineStr">
         <is>
-          <t>Expansion ARR of $869.1K trailed budget $912.6K in June; the -$43.5K shortfall reflects timing of upsell closes and is expected to partially reverse in Q3 as pipeline matures.</t>
+          <t>June Expansion of $869.1K fell short by $43.5K, -4.8% (sheets.arr_waterfall.arr_expansion.period.actual), reflecting slower upsell velocity.</t>
         </is>
       </c>
       <c r="AE7" s="150" t="inlineStr">
         <is>
-          <t>Q2 Expansion of $2.63M vs budget $2.62M, +$9.3K (+0.4%) favorable; the quarter-level result is marginally ahead of plan, indicating the June timing shortfall was offset by stronger earlier-quarter expansion activity.</t>
+          <t>Q2 Expansion of $2.63M slightly beat budget by $9.3K, +0.4% (sheets.arr_waterfall.arr_expansion.qtd.actual), with early-quarter strength compensating for June weakness.</t>
         </is>
       </c>
       <c r="AF7" s="150" t="inlineStr">
         <is>
-          <t>YTD Expansion of $4.78M vs budget $4.71M, +$73.8K (+1.6%) favorable; expansion is tracking above plan through H1 and represents a positive retention signal heading into H2 renewal cycles.</t>
+          <t>YTD Expansion of $4.78M exceeds budget by $73.8K, +1.6% (sheets.arr_waterfall.arr_expansion.ytd.actual), indicating healthy customer expansion trends.</t>
         </is>
       </c>
     </row>
@@ -3831,17 +3812,17 @@
       </c>
       <c r="AD8" s="150" t="inlineStr">
         <is>
-          <t>Reactivation ARR of $142.9K was -$7.1K below budget $150.0K in June; the variance is immaterial and reflects normal monthly variability in win-back activity.</t>
+          <t>June Reactivation of $142.9K missed budget by $7.1K, -4.7% (sheets.arr_waterfall.arr_reactivation.period.actual), showing modest win-back activity.</t>
         </is>
       </c>
       <c r="AE8" s="150" t="inlineStr">
         <is>
-          <t>Q2 Reactivation of $297.9K vs budget $305.0K, -$7.1K (-2.3%) unfavorable; the quarter-level gap mirrors the June shortfall, indicating no meaningful timing offset within Q2 for this motion.</t>
+          <t>Q2 Reactivation of $297.9K fell short by $7.1K, -2.3% (sheets.arr_waterfall.arr_reactivation.qtd.actual), tracking consistently below plan.</t>
         </is>
       </c>
       <c r="AF8" s="150" t="inlineStr">
         <is>
-          <t>YTD Reactivation of $492.9K vs budget $500.0K, -$7.1K (-1.4%) unfavorable; the variance is stable and immaterial; no corrective action required at this scale.</t>
+          <t>YTD Reactivation of $492.9K trails budget by $7.1K, -1.4% (sheets.arr_waterfall.arr_reactivation.ytd.actual), representing a minor headwind to net new ARR.</t>
         </is>
       </c>
     </row>
@@ -3937,17 +3918,17 @@
       </c>
       <c r="AD9" s="150" t="inlineStr">
         <is>
-          <t>Contraction of $313.7K was favorable vs budget $329.3K in June; lower-than-expected downgrades contributed positively to Net New ARR and reflect healthy customer retention behavior.</t>
+          <t>June Contraction of $313.7K beat budget by $15.6K, -4.7% (sheets.arr_waterfall.arr_contraction.period.actual), indicating better-than-expected customer downgrades.</t>
         </is>
       </c>
       <c r="AE9" s="150" t="inlineStr">
         <is>
-          <t>Q2 Contraction of -$778.7K vs budget -$803.6K, +$25.0K (-3.1%) favorable; contraction tracked below budget across Q2, a consistent positive signal for net retention heading into H2.</t>
+          <t>Q2 Contraction of $778.7K beat budget by $25.0K, -3.1% (sheets.arr_waterfall.arr_contraction.qtd.actual), with lower-than-expected downsizes.</t>
         </is>
       </c>
       <c r="AF9" s="150" t="inlineStr">
         <is>
-          <t>YTD Contraction of -$1.36M vs budget -$1.40M, +$36.7K (-2.6%) favorable; the improving trend through H1 supports G$R stability and reduces downside risk to the FY ARR outlook.</t>
+          <t>YTD Contraction of $1.36M beats budget by $36.7K, -2.6% (sheets.arr_waterfall.arr_contraction.ytd.actual), a positive signal for customer health.</t>
         </is>
       </c>
     </row>
@@ -4043,17 +4024,17 @@
       </c>
       <c r="AD10" s="150" t="inlineStr">
         <is>
-          <t>Churn of $520.2K was favorable vs budget $546.2K in June; lower-than-budgeted logo losses contributed +$26.0K to Net New ARR and reflect effective retention efforts in the close month.</t>
+          <t>June Churn of $520.2K beat budget by $26.0K, -4.8% (sheets.arr_waterfall.arr_churn.period.actual), reflecting lower-than-expected customer losses.</t>
         </is>
       </c>
       <c r="AE10" s="150" t="inlineStr">
         <is>
-          <t>Q2 Churn of -$1.48M vs budget -$1.53M, +$54.8K (-3.6%) favorable; churn tracked below budget across the full quarter, the largest single favorable component of the Q2 ARR waterfall.</t>
+          <t>Q2 Churn of $1.48M beat budget by $54.8K, -3.6% (sheets.arr_waterfall.arr_churn.qtd.actual), indicating improving retention.</t>
         </is>
       </c>
       <c r="AF10" s="150" t="inlineStr">
         <is>
-          <t>YTD Churn of -$2.79M vs budget -$2.88M, +$94.0K (-3.3%) favorable; churn is the strongest-performing waterfall component YTD and, if sustained, provides meaningful upside to H2 G$R and N$R metrics.</t>
+          <t>YTD Churn of $2.79M beats budget by $94.0K, -3.3% (sheets.arr_waterfall.arr_churn.ytd.actual), a key driver of YTD Net New ARR outperformance.</t>
         </is>
       </c>
     </row>
@@ -4187,17 +4168,17 @@
       </c>
       <c r="AD13" s="150" t="inlineStr">
         <is>
-          <t>Net New ARR of $1.68M trailed budget $1.77M by -$84.2K in June; New Business and Expansion shortfalls were partially offset by favorable churn and contraction vs budget.</t>
+          <t>June Net New ARR of $1.68M missed budget by $90.0K, -5.1% (sheets.arr_waterfall.arr_net_new.period.actual), driven by New Business shortfall.</t>
         </is>
       </c>
       <c r="AE13" s="150" t="inlineStr">
         <is>
-          <t>Q2 Net New ARR waterfall components net to a favorable quarter vs budget; QTD New Business +$53.8K, Expansion +$9.3K, and Churn +$54.8K more than offset Reactivation -$7.1K, yielding a net positive Q2 ARR outcome.</t>
+          <t>Q2 Net New ARR data not available in this row (sheets.arr_waterfall.arr_net_new.qtd.actual).</t>
         </is>
       </c>
       <c r="AF13" s="150" t="inlineStr">
         <is>
-          <t>YTD Net New ARR waterfall is favorable across all major components; New Business +$215.8K, Expansion +$73.8K, and Churn +$94.0K drive the cumulative +$215.8K YTD Net New ARR outperformance vs budget.</t>
+          <t>YTD Net New ARR data not available in this row (sheets.arr_waterfall.arr_net_new.ytd.actual).</t>
         </is>
       </c>
     </row>
@@ -4293,17 +4274,17 @@
       </c>
       <c r="AD14" s="150" t="inlineStr">
         <is>
-          <t>Ending ARR of $85.31M exceeded budget $84.89M by +$413.1K (+0.5%) in June; favorable churn and contraction more than offset New Business and Expansion shortfalls to deliver an above-budget ARR close.</t>
+          <t>June Ending ARR of $85.31M beat budget by $413.1K, +0.5% (sheets.arr_waterfall.arr_ending.period.actual), with FY 2026 forecast of $90.29M trailing budget $96.10M by $5.81M, -6.0%.</t>
         </is>
       </c>
       <c r="AE14" s="150" t="inlineStr">
         <is>
-          <t>Q2 Ending ARR of $85.31M vs budget $84.89M, +$413.1K (+0.5%) favorable; the quarter closed ahead of plan with ARR momentum supported by below-budget churn across Q2.</t>
+          <t>Q2 Ending ARR of $85.31M beat budget by $413.1K, +0.5% (sheets.arr_waterfall.arr_ending.qtd.actual), consistent with June close.</t>
         </is>
       </c>
       <c r="AF14" s="150" t="inlineStr">
         <is>
-          <t>YTD Ending ARR of $85.31M vs budget $84.89M, +$413.1K favorable; FY outlook of $90.29M trails FY budget $96.10M, indicating H2 New Business must accelerate materially to close the annual ARR gap.</t>
+          <t>YTD Ending ARR of $85.31M beats budget by $413.1K, +0.5% (sheets.arr_waterfall.arr_ending.ytd.actual), though FY 2026 outlook of $90.29M lags budget $96.10M by $5.81M, -6.0%.</t>
         </is>
       </c>
     </row>
@@ -4875,17 +4856,17 @@
       </c>
       <c r="AD5" s="150" t="inlineStr">
         <is>
-          <t>Revenue $7.35M vs budget $7.72M, -$367.5K unfavorable; subscription timing drove the shortfall.</t>
+          <t>June revenue of $7.35M missed budget by $367.5K, -4.8% (sheets.income_statement.is_total_revenue.period.actual), representing 100.0% of total revenue.</t>
         </is>
       </c>
       <c r="AE5" s="150" t="inlineStr">
         <is>
-          <t>Q2 Revenue $21.05M vs budget $22.10M, -$1.05M unfavorable; gap is consistent across Q2, not a single-month timing item.</t>
+          <t>Q2 revenue of $21.05M fell short by $1.05M, -4.8% (sheets.income_statement.is_total_revenue.qtd.actual), at 100.0% of total revenue.</t>
         </is>
       </c>
       <c r="AF5" s="150" t="inlineStr">
         <is>
-          <t>YTD Revenue $39.45M vs budget $41.42M, -$1.97M unfavorable; trend is widening and requires H2 acceleration.</t>
+          <t>YTD revenue of $39.45M trails budget by $1.97M, -4.8% (sheets.income_statement.is_total_revenue.ytd.actual), at 100.0% of total revenue.</t>
         </is>
       </c>
     </row>
@@ -5292,17 +5273,17 @@
       </c>
       <c r="AD11" s="150" t="inlineStr">
         <is>
-          <t>Gross Profit $5.14M vs budget $5.40M, -$257.2K unfavorable; driven by revenue shortfall with margin held flat at 70.0%.</t>
+          <t>June gross profit of $5.14M missed budget by $257.2K, -4.8% (sheets.income_statement.is_gross_profit.period.actual), at 69.9% of revenue.</t>
         </is>
       </c>
       <c r="AE11" s="150" t="inlineStr">
         <is>
-          <t>Q2 Gross Profit $14.87M vs budget $15.62M, -$743.6K unfavorable; margin of 70.7% matched budget, isolating revenue as the sole driver.</t>
+          <t>Q2 gross profit of $14.87M fell short by $743.6K, -4.8% (sheets.income_statement.is_gross_profit.qtd.actual), at 70.6% of revenue.</t>
         </is>
       </c>
       <c r="AF11" s="150" t="inlineStr">
         <is>
-          <t>YTD Gross Profit $27.94M vs budget $29.33M, -$1.40M unfavorable; margin stable at 70.8% vs budget 70.8%; revenue gap is the driver.</t>
+          <t>YTD gross profit of $27.94M trails budget by $1.40M, -4.7% (sheets.income_statement.is_gross_profit.ytd.actual), at 70.8% of revenue.</t>
         </is>
       </c>
     </row>
@@ -5527,17 +5508,17 @@
       </c>
       <c r="AD15" s="150" t="inlineStr">
         <is>
-          <t>S&amp;M $2.50M vs budget $2.65M, -$151.2K favorable; underspend reflects headcount gap and deferred program spend.</t>
+          <t>June S&amp;M of $2.50M came in $151.2K below budget, -5.7% (sheets.income_statement.is_sm.period.actual), at 34.0% of revenue.</t>
         </is>
       </c>
       <c r="AE15" s="150" t="inlineStr">
         <is>
-          <t>Q2 S&amp;M $7.16M vs budget $7.59M, -$433.0K favorable; consistent underspend across Q2 supports EBITDA but risks pipeline coverage.</t>
+          <t>Q2 S&amp;M of $7.16M was $433.0K under budget, -5.7% (sheets.income_statement.is_sm.qtd.actual), at 34.0% of revenue.</t>
         </is>
       </c>
       <c r="AF15" s="150" t="inlineStr">
         <is>
-          <t>YTD S&amp;M $13.41M vs budget $14.22M, -$811.5K favorable; cumulative underspend may constrain H2 pipeline if not redeployed.</t>
+          <t>YTD S&amp;M of $13.41M is $811.5K below budget, -5.7% (sheets.income_statement.is_sm.ytd.actual), at 34.0% of revenue.</t>
         </is>
       </c>
     </row>
@@ -5633,17 +5614,17 @@
       </c>
       <c r="AD16" s="150" t="inlineStr">
         <is>
-          <t>R&amp;D $1.18M vs budget $1.25M, -$71.1K favorable; underspend driven by open headcount and deferred vendor costs.</t>
+          <t>June R&amp;D of $1.18M was $71.1K below budget, -5.6% (sheets.income_statement.is_rd.period.actual), at 16.1% of revenue.</t>
         </is>
       </c>
       <c r="AE16" s="150" t="inlineStr">
         <is>
-          <t>Q2 R&amp;D $3.37M vs budget $3.57M, -$203.8K favorable; underspend is consistent across Q2 and reflects headcount underfill.</t>
+          <t>Q2 R&amp;D of $3.37M fell short by $203.8K, -5.6% (sheets.income_statement.is_rd.qtd.actual), at 16.0% of revenue.</t>
         </is>
       </c>
       <c r="AF16" s="150" t="inlineStr">
         <is>
-          <t>YTD R&amp;D $6.31M vs budget $6.69M, -$381.9K favorable; savings are structural given headcount gap; monitor product delivery risk.</t>
+          <t>YTD R&amp;D of $6.31M trails budget by $381.9K, -5.7% (sheets.income_statement.is_rd.ytd.actual), at 16.0% of revenue.</t>
         </is>
       </c>
     </row>
@@ -5739,17 +5720,17 @@
       </c>
       <c r="AD17" s="150" t="inlineStr">
         <is>
-          <t>G&amp;A $808.5K vs budget $857.4K, -$48.9K favorable; underspend reflects lower professional fees and headcount savings.</t>
+          <t>June G&amp;A of $808.5K came in $48.9K below budget, -5.7% (sheets.income_statement.is_ga.period.actual), at 11.0% of revenue.</t>
         </is>
       </c>
       <c r="AE17" s="150" t="inlineStr">
         <is>
-          <t>Q2 G&amp;A $2.32M vs budget $2.46M, -$140.1K favorable; consistent underspend across Q2 with no unusual timing items.</t>
+          <t>Q2 G&amp;A of $2.32M was $140.1K under budget, -5.7% (sheets.income_statement.is_ga.qtd.actual), at 11.0% of revenue.</t>
         </is>
       </c>
       <c r="AF17" s="150" t="inlineStr">
         <is>
-          <t>YTD G&amp;A $4.34M vs budget $4.60M, -$262.5K favorable; trend is stable; savings are expected to partially reverse as headcount fills in H2.</t>
+          <t>YTD G&amp;A of $4.34M is $262.5K below budget, -5.7% (sheets.income_statement.is_ga.ytd.actual), at 11.0% of revenue.</t>
         </is>
       </c>
     </row>
@@ -5974,17 +5955,17 @@
       </c>
       <c r="AD21" s="150" t="inlineStr">
         <is>
-          <t>EBITDA $661.5K vs budget $647.5K, +$14.0K favorable; opex underspend offset the revenue miss to deliver above-budget profitability.</t>
+          <t>June EBITDA of $661.5K beat budget by $14.0K, +2.2% (sheets.income_statement.is_ebitda.period.actual), at 9.0% of revenue.</t>
         </is>
       </c>
       <c r="AE21" s="150" t="inlineStr">
         <is>
-          <t>Q2 EBITDA $2.03M vs budget $2.00M, +$33.3K favorable; opex discipline across S&amp;M, R&amp;D, and G&amp;A sustained the beat through Q2.</t>
+          <t>Q2 EBITDA of $2.03M exceeded budget by $33.3K, +1.5% (sheets.income_statement.is_ebitda.qtd.actual), at 9.6% of revenue.</t>
         </is>
       </c>
       <c r="AF21" s="150" t="inlineStr">
         <is>
-          <t>YTD EBITDA $3.87M vs budget $3.81M, +$59.1K favorable; trend is stable; FY outlook $7.46M trails FY budget $7.79M by -$328.7K.</t>
+          <t>YTD EBITDA of $3.87M beats budget by $59.1K, +1.6% (sheets.income_statement.is_ebitda.ytd.actual), at 9.8% of revenue.</t>
         </is>
       </c>
     </row>
@@ -6436,88 +6417,88 @@
         </is>
       </c>
       <c r="B5" s="139" t="n">
-        <v>46.103205</v>
+        <v>25.742098</v>
       </c>
       <c r="C5" s="139" t="n">
-        <v>48.709078</v>
+        <v>25.044747</v>
       </c>
       <c r="D5" s="139" t="n">
-        <v>51.011508</v>
+        <v>26.552931</v>
       </c>
       <c r="E5" s="139" t="n">
-        <v>58.094957</v>
+        <v>19.403428</v>
       </c>
       <c r="F5" s="139" t="n">
-        <v>62.571015</v>
+        <v>28.744021</v>
       </c>
       <c r="G5" s="139" t="n">
-        <v>48.0228</v>
+        <v>29.497906</v>
       </c>
       <c r="H5" s="138" t="n">
-        <v>47.895177</v>
+        <v>30</v>
       </c>
       <c r="I5" s="138" t="n">
-        <v>48.212032</v>
+        <v>30.316855</v>
       </c>
       <c r="J5" s="138" t="n">
-        <v>48.537677</v>
+        <v>30.6425</v>
       </c>
       <c r="K5" s="138" t="n">
-        <v>48.871188</v>
+        <v>30.976011</v>
       </c>
       <c r="L5" s="138" t="n">
-        <v>49.213027</v>
+        <v>31.31785</v>
       </c>
       <c r="M5" s="138" t="n">
-        <v>49.562269</v>
+        <v>31.667092</v>
       </c>
       <c r="N5" s="160" t="n">
-        <v>51.011508</v>
+        <v>26.552931</v>
       </c>
       <c r="O5" s="160" t="n">
-        <v>48.0228</v>
+        <v>29.497906</v>
       </c>
       <c r="P5" s="160" t="n">
-        <v>48.0228</v>
+        <v>29.497906</v>
       </c>
       <c r="Q5" s="160" t="n">
-        <v>49.562269</v>
+        <v>31.667092</v>
       </c>
       <c r="R5" s="161" t="n">
-        <v>14.95336</v>
+        <v>26.810706</v>
       </c>
       <c r="S5" s="161" t="n">
-        <v>29.600953</v>
+        <v>27.630607</v>
       </c>
       <c r="T5" s="161" t="n">
-        <v>29.600953</v>
+        <v>27.630607</v>
       </c>
       <c r="U5" s="161" t="n">
-        <v>22.105635</v>
+        <v>29.696912</v>
       </c>
       <c r="V5" s="153" t="n">
-        <v>36.058148</v>
+        <v>-0.2577749999999988</v>
       </c>
       <c r="W5" s="153" t="n">
-        <v>18.421847</v>
+        <v>1.867298999999999</v>
       </c>
       <c r="X5" s="153" t="n">
-        <v>18.421847</v>
+        <v>1.867298999999999</v>
       </c>
       <c r="Y5" s="153" t="n">
-        <v>27.456634</v>
+        <v>1.970179999999999</v>
       </c>
       <c r="Z5" s="154" t="n">
-        <v>2.411374299822916</v>
+        <v>-0.009614629320093203</v>
       </c>
       <c r="AA5" s="154" t="n">
-        <v>0.6223396591319204</v>
+        <v>0.06758081717133464</v>
       </c>
       <c r="AB5" s="154" t="n">
-        <v>0.6223396591319204</v>
+        <v>0.06758081717133464</v>
       </c>
       <c r="AC5" s="154" t="n">
-        <v>1.242064930503014</v>
+        <v>0.06634292481319266</v>
       </c>
     </row>
     <row r="6" ht="6" customHeight="1" s="122">
@@ -6565,22 +6546,22 @@
         </is>
       </c>
       <c r="B8" s="143" t="n">
-        <v>9.274473</v>
+        <v>10.427217</v>
       </c>
       <c r="C8" s="143" t="n">
-        <v>8.667528000000001</v>
+        <v>10.032076</v>
       </c>
       <c r="D8" s="143" t="n">
-        <v>13.591547</v>
+        <v>1.368911</v>
       </c>
       <c r="E8" s="143" t="n">
-        <v>10.820161</v>
+        <v>17.77795</v>
       </c>
       <c r="F8" s="143" t="n">
-        <v>9.651536999999999</v>
+        <v>8.925884999999999</v>
       </c>
       <c r="G8" s="143" t="n">
-        <v>6.814083</v>
+        <v>7.128503</v>
       </c>
       <c r="H8" s="144" t="n">
         <v>7.27048</v>
@@ -6601,16 +6582,16 @@
         <v>8.36434</v>
       </c>
       <c r="N8" s="156" t="n">
-        <v>31.533548</v>
+        <v>21.828204</v>
       </c>
       <c r="O8" s="156" t="n">
-        <v>27.285781</v>
+        <v>33.832338</v>
       </c>
       <c r="P8" s="156" t="n">
-        <v>58.819329</v>
+        <v>55.660542</v>
       </c>
       <c r="Q8" s="156" t="n">
-        <v>106.162549</v>
+        <v>103.003762</v>
       </c>
       <c r="R8" s="145" t="n">
         <v>31.533548</v>
@@ -6625,28 +6606,28 @@
         <v>99.72130900000001</v>
       </c>
       <c r="V8" s="151" t="n">
-        <v>0</v>
+        <v>-9.705344000000004</v>
       </c>
       <c r="W8" s="147" t="n">
-        <v>-2.100189</v>
+        <v>4.446368</v>
       </c>
       <c r="X8" s="147" t="n">
-        <v>-2.100189</v>
+        <v>-5.258976000000004</v>
       </c>
       <c r="Y8" s="146" t="n">
-        <v>6.441239999999993</v>
+        <v>3.28245299999999</v>
       </c>
       <c r="Z8" s="152" t="n">
-        <v>0</v>
+        <v>-0.3077783698808648</v>
       </c>
       <c r="AA8" s="149" t="n">
-        <v>-0.0714691058351996</v>
+        <v>0.1513092132061661</v>
       </c>
       <c r="AB8" s="149" t="n">
-        <v>-0.03447481314609219</v>
+        <v>-0.08632661867088318</v>
       </c>
       <c r="AC8" s="148" t="n">
-        <v>0.06459241324238928</v>
+        <v>0.03291626466716346</v>
       </c>
     </row>
     <row r="9" ht="6" customHeight="1" s="122">
@@ -6876,19 +6857,19 @@
         </is>
       </c>
       <c r="B13" s="143" t="n">
-        <v>1.375</v>
+        <v>5.892967</v>
       </c>
       <c r="C13" s="143" t="n">
-        <v>1.378429</v>
+        <v>3.595225</v>
       </c>
       <c r="D13" s="143" t="n">
-        <v>1.370333</v>
+        <v>3.432649</v>
       </c>
       <c r="E13" s="143" t="n">
-        <v>1.359349</v>
+        <v>3.498603</v>
       </c>
       <c r="F13" s="143" t="n">
-        <v>1.362448</v>
+        <v>3.389018</v>
       </c>
       <c r="G13" s="143" t="n">
         <v>3.662494</v>
@@ -6912,16 +6893,16 @@
         <v>4.915371</v>
       </c>
       <c r="N13" s="156" t="n">
-        <v>4.123762</v>
+        <v>12.920841</v>
       </c>
       <c r="O13" s="156" t="n">
-        <v>6.384291</v>
+        <v>10.550115</v>
       </c>
       <c r="P13" s="156" t="n">
-        <v>10.508053</v>
+        <v>23.470956</v>
       </c>
       <c r="Q13" s="156" t="n">
-        <v>39.562368</v>
+        <v>52.525271</v>
       </c>
       <c r="R13" s="162" t="n">
         <v>4.144171999999999</v>
@@ -6936,28 +6917,28 @@
         <v>16.824142</v>
       </c>
       <c r="V13" s="151" t="n">
-        <v>-0.02040999999999915</v>
+        <v>8.776669</v>
       </c>
       <c r="W13" s="146" t="n">
-        <v>2.185193</v>
+        <v>6.351017</v>
       </c>
       <c r="X13" s="146" t="n">
-        <v>2.164783</v>
+        <v>15.127686</v>
       </c>
       <c r="Y13" s="146" t="n">
-        <v>22.738226</v>
+        <v>35.70112900000001</v>
       </c>
       <c r="Z13" s="152" t="n">
-        <v>-0.004924988634641408</v>
+        <v>2.117834153601733</v>
       </c>
       <c r="AA13" s="148" t="n">
-        <v>0.5203958088141786</v>
+        <v>1.512471726070694</v>
       </c>
       <c r="AB13" s="148" t="n">
-        <v>0.259464574441436</v>
+        <v>1.813160307649159</v>
       </c>
       <c r="AC13" s="148" t="n">
-        <v>1.351523661652404</v>
+        <v>2.122017812260501</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1" s="122">
@@ -7240,22 +7221,22 @@
         </is>
       </c>
       <c r="B17" s="143" t="n">
-        <v>0.18</v>
+        <v>0.118</v>
       </c>
       <c r="C17" s="143" t="n">
-        <v>0.18</v>
+        <v>0.122</v>
       </c>
       <c r="D17" s="143" t="n">
-        <v>0.18</v>
+        <v>0.128</v>
       </c>
       <c r="E17" s="143" t="n">
-        <v>0.18</v>
+        <v>0.134</v>
       </c>
       <c r="F17" s="143" t="n">
-        <v>0.18</v>
+        <v>0.14</v>
       </c>
       <c r="G17" s="143" t="n">
-        <v>-0.22</v>
+        <v>0.147</v>
       </c>
       <c r="H17" s="144" t="n">
         <v>-0.153816</v>
@@ -7276,16 +7257,16 @@
         <v>-0.171564</v>
       </c>
       <c r="N17" s="156" t="n">
-        <v>0.54</v>
+        <v>0.368</v>
       </c>
       <c r="O17" s="156" t="n">
-        <v>0.14</v>
+        <v>0.421</v>
       </c>
       <c r="P17" s="156" t="n">
-        <v>0.6799999999999999</v>
+        <v>0.789</v>
       </c>
       <c r="Q17" s="156" t="n">
-        <v>-0.29716</v>
+        <v>-0.18816</v>
       </c>
       <c r="R17" s="162" t="n">
         <v>0.54</v>
@@ -7300,28 +7281,28 @@
         <v>2.65</v>
       </c>
       <c r="V17" s="151" t="n">
-        <v>0</v>
+        <v>-0.172</v>
       </c>
       <c r="W17" s="146" t="n">
-        <v>-0.4399999999999999</v>
+        <v>-0.1589999999999999</v>
       </c>
       <c r="X17" s="146" t="n">
-        <v>-0.4399999999999999</v>
+        <v>-0.3309999999999998</v>
       </c>
       <c r="Y17" s="151" t="n">
-        <v>-2.94716</v>
+        <v>-2.83816</v>
       </c>
       <c r="Z17" s="152" t="n">
-        <v>0</v>
+        <v>-0.3185185185185186</v>
       </c>
       <c r="AA17" s="148" t="n">
-        <v>-0.7586206896551724</v>
+        <v>-0.2741379310344826</v>
       </c>
       <c r="AB17" s="148" t="n">
-        <v>-0.3928571428571428</v>
+        <v>-0.2955357142857142</v>
       </c>
       <c r="AC17" s="152" t="n">
-        <v>-1.112135849056604</v>
+        <v>-1.071003773584906</v>
       </c>
     </row>
     <row r="18" ht="6" customHeight="1" s="122">
@@ -7582,88 +7563,88 @@
         </is>
       </c>
       <c r="B23" s="137" t="n">
-        <v>48.709078</v>
+        <v>25.044747</v>
       </c>
       <c r="C23" s="137" t="n">
-        <v>51.011508</v>
+        <v>26.552931</v>
       </c>
       <c r="D23" s="137" t="n">
-        <v>58.094957</v>
+        <v>19.403428</v>
       </c>
       <c r="E23" s="137" t="n">
-        <v>62.571015</v>
+        <v>28.744021</v>
       </c>
       <c r="F23" s="137" t="n">
-        <v>66.037122</v>
+        <v>29.497906</v>
       </c>
       <c r="G23" s="137" t="n">
-        <v>48.4318</v>
+        <v>30</v>
       </c>
       <c r="H23" s="138" t="n">
-        <v>48.212032</v>
+        <v>30.316855</v>
       </c>
       <c r="I23" s="138" t="n">
-        <v>48.537677</v>
+        <v>30.6425</v>
       </c>
       <c r="J23" s="138" t="n">
-        <v>48.871188</v>
+        <v>30.976011</v>
       </c>
       <c r="K23" s="138" t="n">
-        <v>49.213027</v>
+        <v>31.31785</v>
       </c>
       <c r="L23" s="138" t="n">
-        <v>49.562269</v>
+        <v>31.667092</v>
       </c>
       <c r="M23" s="138" t="n">
-        <v>49.919376</v>
+        <v>32.024199</v>
       </c>
       <c r="N23" s="160" t="n">
-        <v>58.094957</v>
+        <v>19.403428</v>
       </c>
       <c r="O23" s="160" t="n">
-        <v>48.4318</v>
+        <v>30</v>
       </c>
       <c r="P23" s="160" t="n">
-        <v>48.4318</v>
+        <v>30</v>
       </c>
       <c r="Q23" s="160" t="n">
-        <v>49.919376</v>
+        <v>32.024199</v>
       </c>
       <c r="R23" s="140" t="n">
-        <v>21.922814</v>
+        <v>27.060234</v>
       </c>
       <c r="S23" s="140" t="n">
-        <v>31.455591</v>
+        <v>27.90735</v>
       </c>
       <c r="T23" s="140" t="n">
-        <v>31.455591</v>
+        <v>27.90735</v>
       </c>
       <c r="U23" s="140" t="n">
-        <v>23.85061</v>
+        <v>30.08828</v>
       </c>
       <c r="V23" s="153" t="n">
-        <v>36.17214300000001</v>
+        <v>-7.656806</v>
       </c>
       <c r="W23" s="153" t="n">
-        <v>16.976209</v>
+        <v>2.092649999999999</v>
       </c>
       <c r="X23" s="153" t="n">
-        <v>16.976209</v>
+        <v>2.092649999999999</v>
       </c>
       <c r="Y23" s="153" t="n">
-        <v>26.068766</v>
+        <v>1.935919000000002</v>
       </c>
       <c r="Z23" s="154" t="n">
-        <v>1.649977188147471</v>
+        <v>-0.2829541680977333</v>
       </c>
       <c r="AA23" s="154" t="n">
-        <v>0.5396881273030287</v>
+        <v>0.07498562206730482</v>
       </c>
       <c r="AB23" s="154" t="n">
-        <v>0.5396881273030287</v>
+        <v>0.07498562206730482</v>
       </c>
       <c r="AC23" s="154" t="n">
-        <v>1.093002065775257</v>
+        <v>0.06434129833941993</v>
       </c>
     </row>
     <row r="24" ht="17" customHeight="1" s="122">
@@ -7896,7 +7877,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF28"/>
+  <dimension ref="A1:AJ28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="36.54296875" bestFit="1" customWidth="1" style="122" min="1" max="1"/>
@@ -8098,21 +8079,6 @@
 Var %</t>
         </is>
       </c>
-      <c r="AD3" s="136" t="inlineStr">
-        <is>
-          <t>Period vs Budget Commentary</t>
-        </is>
-      </c>
-      <c r="AE3" s="136" t="inlineStr">
-        <is>
-          <t>QTD vs Budget Commentary</t>
-        </is>
-      </c>
-      <c r="AF3" s="136" t="inlineStr">
-        <is>
-          <t>YTD vs Budget Commentary</t>
-        </is>
-      </c>
     </row>
     <row r="4" ht="16" customHeight="1" s="122">
       <c r="A4" s="99" t="inlineStr">
@@ -8309,8 +8275,8 @@
           <t>Change in AR / Collections vs Revenue</t>
         </is>
       </c>
-      <c r="B7" s="12" t="n">
-        <v>2.68</v>
+      <c r="B7" s="143" t="n">
+        <v>1.153659</v>
       </c>
       <c r="C7" s="143" t="n">
         <v>1.249179</v>
@@ -8346,52 +8312,52 @@
         <v>-0.209667</v>
       </c>
       <c r="N7" s="156" t="n">
-        <v>-6.446996</v>
+        <v>-5.293337</v>
       </c>
       <c r="O7" s="156" t="n">
         <v>8.641434</v>
       </c>
       <c r="P7" s="156" t="n">
-        <v>2.194438</v>
+        <v>3.348097</v>
       </c>
       <c r="Q7" s="156" t="n">
-        <v>0.8871050000000003</v>
+        <v>2.040764</v>
       </c>
       <c r="R7" s="145" t="n">
-        <v>-0.6475</v>
+        <v>4.125097</v>
       </c>
       <c r="S7" s="145" t="n">
         <v>-1.23025</v>
       </c>
       <c r="T7" s="145" t="n">
-        <v>-1.87775</v>
+        <v>2.894847</v>
       </c>
       <c r="U7" s="145" t="n">
-        <v>-3.146727</v>
+        <v>1.62587</v>
       </c>
       <c r="V7" s="147" t="n">
-        <v>-5.799496</v>
+        <v>-9.418434000000001</v>
       </c>
       <c r="W7" s="147" t="n">
         <v>9.871684</v>
       </c>
       <c r="X7" s="147" t="n">
-        <v>4.072188000000001</v>
+        <v>0.4532499999999997</v>
       </c>
       <c r="Y7" s="146" t="n">
-        <v>4.033832</v>
+        <v>0.4148940000000001</v>
       </c>
       <c r="Z7" s="149" t="n">
-        <v>8.956750579150579</v>
+        <v>-2.283203037407363</v>
       </c>
       <c r="AA7" s="149" t="n">
         <v>-8.02412842918106</v>
       </c>
       <c r="AB7" s="149" t="n">
-        <v>-2.168652909066703</v>
+        <v>0.156571314477069</v>
       </c>
       <c r="AC7" s="148" t="n">
-        <v>-1.281913556530325</v>
+        <v>0.2551827636895939</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1" s="122">
@@ -8400,8 +8366,8 @@
           <t>Change in Deferred Revenue</t>
         </is>
       </c>
-      <c r="B8" s="12" t="n">
-        <v>2.68</v>
+      <c r="B8" s="143" t="n">
+        <v>0.044</v>
       </c>
       <c r="C8" s="143" t="n">
         <v>0.032</v>
@@ -8437,52 +8403,52 @@
         <v>0.06773700000000001</v>
       </c>
       <c r="N8" s="156" t="n">
-        <v>0.08</v>
+        <v>0.124</v>
       </c>
       <c r="O8" s="156" t="n">
         <v>0.152</v>
       </c>
       <c r="P8" s="156" t="n">
-        <v>0.232</v>
+        <v>0.276</v>
       </c>
       <c r="Q8" s="156" t="n">
-        <v>0.596272</v>
+        <v>0.640272</v>
       </c>
       <c r="R8" s="145" t="n">
-        <v>0.092721</v>
+        <v>0.135921</v>
       </c>
       <c r="S8" s="145" t="n">
         <v>0.156447</v>
       </c>
       <c r="T8" s="145" t="n">
-        <v>0.249168</v>
+        <v>0.292368</v>
       </c>
       <c r="U8" s="145" t="n">
-        <v>0.636512</v>
+        <v>0.679712</v>
       </c>
       <c r="V8" s="146" t="n">
-        <v>-0.012721</v>
+        <v>-0.01192100000000001</v>
       </c>
       <c r="W8" s="146" t="n">
         <v>-0.004447000000000007</v>
       </c>
       <c r="X8" s="146" t="n">
-        <v>-0.01716799999999999</v>
+        <v>-0.01636799999999999</v>
       </c>
       <c r="Y8" s="146" t="n">
-        <v>-0.04023999999999994</v>
+        <v>-0.03944000000000003</v>
       </c>
       <c r="Z8" s="148" t="n">
-        <v>-0.1371965358440914</v>
+        <v>-0.08770535825957736</v>
       </c>
       <c r="AA8" s="148" t="n">
         <v>-0.02842496180815232</v>
       </c>
       <c r="AB8" s="148" t="n">
-        <v>-0.068901303538175</v>
+        <v>-0.05598423904120831</v>
       </c>
       <c r="AC8" s="148" t="n">
-        <v>-0.06321954652858068</v>
+        <v>-0.05802457511416605</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1" s="122">
@@ -8491,8 +8457,8 @@
           <t>Change in AP &amp; Accrued Liabilities</t>
         </is>
       </c>
-      <c r="B9" s="12" t="n">
-        <v>-0.06899999999999999</v>
+      <c r="B9" s="143" t="n">
+        <v>-2.278709</v>
       </c>
       <c r="C9" s="143" t="n">
         <v>-0.171295</v>
@@ -8528,52 +8494,52 @@
         <v>0.099068</v>
       </c>
       <c r="N9" s="156" t="n">
-        <v>-0.092823</v>
+        <v>-2.371532</v>
       </c>
       <c r="O9" s="156" t="n">
         <v>0.466288</v>
       </c>
       <c r="P9" s="156" t="n">
-        <v>0.373465</v>
+        <v>-1.905244</v>
       </c>
       <c r="Q9" s="156" t="n">
-        <v>-0.774385</v>
+        <v>-3.053094</v>
       </c>
       <c r="R9" s="145" t="n">
-        <v>0.299693</v>
+        <v>-4.117959</v>
       </c>
       <c r="S9" s="145" t="n">
         <v>0.6180369999999999</v>
       </c>
       <c r="T9" s="145" t="n">
-        <v>0.91773</v>
+        <v>-3.499922</v>
       </c>
       <c r="U9" s="145" t="n">
-        <v>1.533592</v>
+        <v>-2.88406</v>
       </c>
       <c r="V9" s="147" t="n">
-        <v>-0.392516</v>
+        <v>1.746427</v>
       </c>
       <c r="W9" s="147" t="n">
         <v>-0.151749</v>
       </c>
       <c r="X9" s="147" t="n">
-        <v>-0.544265</v>
+        <v>1.594678</v>
       </c>
       <c r="Y9" s="147" t="n">
-        <v>-2.307977</v>
+        <v>-0.1690339999999999</v>
       </c>
       <c r="Z9" s="149" t="n">
-        <v>-1.309726953916174</v>
+        <v>-0.4241001428134665</v>
       </c>
       <c r="AA9" s="149" t="n">
         <v>-0.2455338434430301</v>
       </c>
       <c r="AB9" s="149" t="n">
-        <v>-0.5930556917611933</v>
+        <v>-0.4556324398086586</v>
       </c>
       <c r="AC9" s="149" t="n">
-        <v>-1.504948513033453</v>
+        <v>0.05860973766149105</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1" s="122">
@@ -8705,88 +8671,88 @@
         </is>
       </c>
       <c r="B12" s="137" t="n">
-        <v>0.4577</v>
+        <v>-0.57935</v>
       </c>
       <c r="C12" s="137" t="n">
-        <v>1.599183</v>
+        <v>1.630183</v>
       </c>
       <c r="D12" s="137" t="n">
-        <v>-7.055503</v>
+        <v>-7.021503</v>
       </c>
       <c r="E12" s="137" t="n">
-        <v>9.437593</v>
+        <v>9.474593</v>
       </c>
       <c r="F12" s="137" t="n">
-        <v>0.853885</v>
+        <v>0.893885</v>
       </c>
       <c r="G12" s="137" t="n">
-        <v>0.605594</v>
+        <v>0.6490939999999999</v>
       </c>
       <c r="H12" s="138" t="n">
-        <v>-1.377632</v>
+        <v>-1.332232</v>
       </c>
       <c r="I12" s="138" t="n">
-        <v>0.402324</v>
+        <v>0.449624</v>
       </c>
       <c r="J12" s="138" t="n">
-        <v>0.428638</v>
+        <v>0.477638</v>
       </c>
       <c r="K12" s="138" t="n">
-        <v>0.436155</v>
+        <v>0.486955</v>
       </c>
       <c r="L12" s="138" t="n">
-        <v>0.462114</v>
+        <v>0.514514</v>
       </c>
       <c r="M12" s="138" t="n">
-        <v>0.469287</v>
+        <v>0.523387</v>
       </c>
       <c r="N12" s="155" t="n">
-        <v>-4.99862</v>
+        <v>-5.97067</v>
       </c>
       <c r="O12" s="155" t="n">
-        <v>10.897072</v>
+        <v>11.017572</v>
       </c>
       <c r="P12" s="155" t="n">
-        <v>5.898452</v>
+        <v>5.046902</v>
       </c>
       <c r="Q12" s="155" t="n">
-        <v>6.719338</v>
+        <v>6.166788</v>
       </c>
       <c r="R12" s="140" t="n">
-        <v>1.188191</v>
+        <v>1.704537</v>
       </c>
       <c r="S12" s="140" t="n">
-        <v>1.15814</v>
+        <v>1.289165</v>
       </c>
       <c r="T12" s="140" t="n">
-        <v>2.346331</v>
+        <v>2.993702</v>
       </c>
       <c r="U12" s="140" t="n">
-        <v>5.3041</v>
+        <v>6.269631</v>
       </c>
       <c r="V12" s="153" t="n">
-        <v>-6.186811</v>
+        <v>-7.675207</v>
       </c>
       <c r="W12" s="141" t="n">
-        <v>9.738932</v>
+        <v>9.728407000000001</v>
       </c>
       <c r="X12" s="141" t="n">
-        <v>3.552121</v>
+        <v>2.0532</v>
       </c>
       <c r="Y12" s="153" t="n">
-        <v>1.415238</v>
+        <v>-0.102843</v>
       </c>
       <c r="Z12" s="154" t="n">
-        <v>-5.20691622811484</v>
+        <v>-4.502810440606452</v>
       </c>
       <c r="AA12" s="142" t="n">
-        <v>8.409114614813408</v>
+        <v>7.546285386277164</v>
       </c>
       <c r="AB12" s="142" t="n">
-        <v>1.513904474688354</v>
+        <v>0.6858398063668329</v>
       </c>
       <c r="AC12" s="154" t="n">
-        <v>0.2668196300974717</v>
+        <v>-0.01640335770956856</v>
       </c>
     </row>
     <row r="13" ht="6" customHeight="1" s="122">
@@ -8833,89 +8799,89 @@
           <t>Capital Expenditures (CapEx)</t>
         </is>
       </c>
-      <c r="B15" s="12" t="n">
-        <v>-0.18</v>
+      <c r="B15" s="143" t="n">
+        <v>-0.118</v>
       </c>
       <c r="C15" s="143" t="n">
-        <v>-0.061</v>
+        <v>-0.122</v>
       </c>
       <c r="D15" s="143" t="n">
-        <v>-0.064</v>
+        <v>-0.128</v>
       </c>
       <c r="E15" s="143" t="n">
-        <v>-0.067</v>
+        <v>-0.134</v>
       </c>
       <c r="F15" s="143" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.14</v>
       </c>
       <c r="G15" s="143" t="n">
-        <v>-0.0735</v>
+        <v>-0.147</v>
       </c>
       <c r="H15" s="144" t="n">
-        <v>-0.0455</v>
+        <v>-0.175</v>
       </c>
       <c r="I15" s="144" t="n">
-        <v>-0.0475</v>
+        <v>-0.178</v>
       </c>
       <c r="J15" s="144" t="n">
-        <v>-0.0495</v>
+        <v>-0.181</v>
       </c>
       <c r="K15" s="144" t="n">
-        <v>-0.0515</v>
+        <v>-0.184</v>
       </c>
       <c r="L15" s="144" t="n">
-        <v>-0.0535</v>
+        <v>-0.187</v>
       </c>
       <c r="M15" s="144" t="n">
-        <v>-0.0555</v>
+        <v>-0.19</v>
       </c>
       <c r="N15" s="156" t="n">
-        <v>-0.125</v>
+        <v>-0.368</v>
       </c>
       <c r="O15" s="156" t="n">
-        <v>-0.2105</v>
+        <v>-0.421</v>
       </c>
       <c r="P15" s="156" t="n">
-        <v>-0.3355</v>
+        <v>-0.789</v>
       </c>
       <c r="Q15" s="156" t="n">
-        <v>-0.6385</v>
+        <v>-1.884</v>
       </c>
       <c r="R15" s="145" t="n">
-        <v>-0.13125</v>
+        <v>-0.3864</v>
       </c>
       <c r="S15" s="145" t="n">
-        <v>-0.221025</v>
+        <v>-0.4420499999999999</v>
       </c>
       <c r="T15" s="145" t="n">
-        <v>-0.352275</v>
+        <v>-0.8284499999999999</v>
       </c>
       <c r="U15" s="145" t="n">
-        <v>-0.670275</v>
+        <v>-1.92345</v>
       </c>
       <c r="V15" s="151" t="n">
-        <v>0.006249999999999978</v>
+        <v>0.01839999999999997</v>
       </c>
       <c r="W15" s="147" t="n">
-        <v>0.01052499999999995</v>
+        <v>0.0210499999999999</v>
       </c>
       <c r="X15" s="147" t="n">
-        <v>0.01677499999999998</v>
+        <v>0.03944999999999987</v>
       </c>
       <c r="Y15" s="151" t="n">
-        <v>0.031775</v>
+        <v>0.03944999999999999</v>
       </c>
       <c r="Z15" s="152" t="n">
-        <v>-0.04761904761904746</v>
+        <v>-0.04761904761904755</v>
       </c>
       <c r="AA15" s="149" t="n">
         <v>-0.0476190476190474</v>
       </c>
       <c r="AB15" s="149" t="n">
-        <v>-0.04761904761904757</v>
+        <v>-0.04761904761904747</v>
       </c>
       <c r="AC15" s="152" t="n">
-        <v>-0.04740591548245123</v>
+        <v>-0.02051002105591515</v>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1" s="122">
@@ -8924,89 +8890,89 @@
           <t>Cash from Investing (CFI)</t>
         </is>
       </c>
-      <c r="B16" s="108" t="n">
-        <v>-0.18</v>
+      <c r="B16" s="137" t="n">
+        <v>-0.118</v>
       </c>
       <c r="C16" s="137" t="n">
-        <v>-0.061</v>
+        <v>-0.122</v>
       </c>
       <c r="D16" s="137" t="n">
-        <v>-0.064</v>
+        <v>-0.128</v>
       </c>
       <c r="E16" s="137" t="n">
-        <v>-0.067</v>
+        <v>-0.134</v>
       </c>
       <c r="F16" s="137" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.14</v>
       </c>
       <c r="G16" s="137" t="n">
-        <v>-0.0735</v>
+        <v>-0.147</v>
       </c>
       <c r="H16" s="138" t="n">
-        <v>-0.0455</v>
+        <v>-0.175</v>
       </c>
       <c r="I16" s="138" t="n">
-        <v>-0.0475</v>
+        <v>-0.178</v>
       </c>
       <c r="J16" s="138" t="n">
-        <v>-0.0495</v>
+        <v>-0.181</v>
       </c>
       <c r="K16" s="138" t="n">
-        <v>-0.0515</v>
+        <v>-0.184</v>
       </c>
       <c r="L16" s="138" t="n">
-        <v>-0.0535</v>
+        <v>-0.187</v>
       </c>
       <c r="M16" s="138" t="n">
-        <v>-0.0555</v>
+        <v>-0.19</v>
       </c>
       <c r="N16" s="155" t="n">
-        <v>-0.125</v>
+        <v>-0.368</v>
       </c>
       <c r="O16" s="155" t="n">
-        <v>-0.2105</v>
+        <v>-0.421</v>
       </c>
       <c r="P16" s="155" t="n">
-        <v>-0.3355</v>
+        <v>-0.789</v>
       </c>
       <c r="Q16" s="155" t="n">
-        <v>-0.6385</v>
+        <v>-1.884</v>
       </c>
       <c r="R16" s="140" t="n">
-        <v>-0.13125</v>
+        <v>-0.3864</v>
       </c>
       <c r="S16" s="140" t="n">
-        <v>-0.221025</v>
+        <v>-0.4420499999999999</v>
       </c>
       <c r="T16" s="140" t="n">
-        <v>-0.352275</v>
+        <v>-0.8284499999999999</v>
       </c>
       <c r="U16" s="140" t="n">
-        <v>-0.670275</v>
+        <v>-1.92345</v>
       </c>
       <c r="V16" s="158" t="n">
-        <v>0.006249999999999978</v>
+        <v>0.01839999999999997</v>
       </c>
       <c r="W16" s="153" t="n">
-        <v>0.01052499999999995</v>
+        <v>0.0210499999999999</v>
       </c>
       <c r="X16" s="153" t="n">
-        <v>0.01677499999999998</v>
+        <v>0.03944999999999987</v>
       </c>
       <c r="Y16" s="158" t="n">
-        <v>0.031775</v>
+        <v>0.03944999999999999</v>
       </c>
       <c r="Z16" s="159" t="n">
-        <v>-0.04761904761904746</v>
+        <v>-0.04761904761904755</v>
       </c>
       <c r="AA16" s="154" t="n">
         <v>-0.0476190476190474</v>
       </c>
       <c r="AB16" s="154" t="n">
-        <v>-0.04761904761904757</v>
+        <v>-0.04761904761904747</v>
       </c>
       <c r="AC16" s="159" t="n">
-        <v>-0.04740591548245123</v>
+        <v>-0.02051002105591515</v>
       </c>
     </row>
     <row r="17" ht="6" customHeight="1" s="122">
@@ -9235,7 +9201,7 @@
           <t>Cash from Financing (CFF)</t>
         </is>
       </c>
-      <c r="B21" s="115" t="n">
+      <c r="B21" s="163" t="n">
         <v>0</v>
       </c>
       <c r="C21" s="163" t="n">
@@ -9364,8 +9330,8 @@
           <t>Net Change in Cash</t>
         </is>
       </c>
-      <c r="B24" s="108" t="n">
-        <v>2.578999999999999</v>
+      <c r="B24" s="137" t="n">
+        <v>-0.69735</v>
       </c>
       <c r="C24" s="137" t="n">
         <v>1.508183</v>
@@ -9401,52 +9367,52 @@
         <v>0.333387</v>
       </c>
       <c r="N24" s="155" t="n">
-        <v>-5.64132</v>
+        <v>-6.33867</v>
       </c>
       <c r="O24" s="155" t="n">
         <v>10.596572</v>
       </c>
       <c r="P24" s="155" t="n">
-        <v>4.955252</v>
+        <v>4.257902</v>
       </c>
       <c r="Q24" s="155" t="n">
-        <v>4.980138</v>
+        <v>4.282788</v>
       </c>
       <c r="R24" s="140" t="n">
-        <v>0.544988</v>
+        <v>1.318137</v>
       </c>
       <c r="S24" s="140" t="n">
         <v>0.8471150000000001</v>
       </c>
       <c r="T24" s="140" t="n">
-        <v>1.392103</v>
+        <v>2.165252</v>
       </c>
       <c r="U24" s="140" t="n">
-        <v>3.573032</v>
+        <v>4.346181</v>
       </c>
       <c r="V24" s="153" t="n">
-        <v>-6.186308</v>
+        <v>-7.656807000000001</v>
       </c>
       <c r="W24" s="141" t="n">
         <v>9.749457</v>
       </c>
       <c r="X24" s="141" t="n">
-        <v>3.563149</v>
+        <v>2.092649999999999</v>
       </c>
       <c r="Y24" s="153" t="n">
-        <v>1.407106</v>
+        <v>-0.06339299999999959</v>
       </c>
       <c r="Z24" s="154" t="n">
-        <v>-11.35127378951463</v>
+        <v>-5.80880970642657</v>
       </c>
       <c r="AA24" s="142" t="n">
         <v>11.5090123536946</v>
       </c>
       <c r="AB24" s="142" t="n">
-        <v>2.559544085459193</v>
+        <v>0.9664694917727817</v>
       </c>
       <c r="AC24" s="154" t="n">
-        <v>0.3938128737721913</v>
+        <v>-0.01458590887033918</v>
       </c>
     </row>
     <row r="25" ht="17" customHeight="1" s="122">
@@ -9455,89 +9421,89 @@
           <t>Beginning Cash Balance</t>
         </is>
       </c>
-      <c r="B25" s="12" t="n">
-        <v>46.1</v>
+      <c r="B25" s="143" t="n">
+        <v>25.742098</v>
       </c>
       <c r="C25" s="143" t="n">
-        <v>45.30265</v>
+        <v>25.044747</v>
       </c>
       <c r="D25" s="143" t="n">
-        <v>46.810833</v>
+        <v>26.552931</v>
       </c>
       <c r="E25" s="143" t="n">
-        <v>39.66133</v>
+        <v>19.403428</v>
       </c>
       <c r="F25" s="143" t="n">
-        <v>49.001923</v>
+        <v>28.744021</v>
       </c>
       <c r="G25" s="143" t="n">
-        <v>49.755808</v>
+        <v>29.497906</v>
       </c>
       <c r="H25" s="144" t="n">
-        <v>50.257902</v>
+        <v>30</v>
       </c>
       <c r="I25" s="144" t="n">
-        <v>48.750671</v>
+        <v>28.492768</v>
       </c>
       <c r="J25" s="144" t="n">
-        <v>49.022294</v>
+        <v>28.764392</v>
       </c>
       <c r="K25" s="144" t="n">
-        <v>49.318932</v>
+        <v>29.06103</v>
       </c>
       <c r="L25" s="144" t="n">
-        <v>49.621887</v>
+        <v>29.363985</v>
       </c>
       <c r="M25" s="144" t="n">
-        <v>49.949402</v>
+        <v>29.691499</v>
       </c>
       <c r="N25" s="156" t="n">
-        <v>46.810833</v>
+        <v>26.552931</v>
       </c>
       <c r="O25" s="156" t="n">
-        <v>49.755808</v>
+        <v>29.497906</v>
       </c>
       <c r="P25" s="156" t="n">
-        <v>49.755808</v>
+        <v>29.497906</v>
       </c>
       <c r="Q25" s="156" t="n">
-        <v>49.949402</v>
+        <v>29.691499</v>
       </c>
       <c r="R25" s="145" t="n">
-        <v>47.068608</v>
+        <v>26.810706</v>
       </c>
       <c r="S25" s="145" t="n">
-        <v>47.888509</v>
+        <v>27.630607</v>
       </c>
       <c r="T25" s="145" t="n">
-        <v>47.888509</v>
+        <v>27.630607</v>
       </c>
       <c r="U25" s="145" t="n">
-        <v>49.954814</v>
+        <v>29.696912</v>
       </c>
       <c r="V25" s="146" t="n">
-        <v>-0.2577749999999952</v>
+        <v>-0.2577749999999988</v>
       </c>
       <c r="W25" s="146" t="n">
-        <v>1.867299000000003</v>
+        <v>1.867298999999999</v>
       </c>
       <c r="X25" s="146" t="n">
-        <v>1.867299000000003</v>
+        <v>1.867298999999999</v>
       </c>
       <c r="Y25" s="146" t="n">
-        <v>-0.00541199999999975</v>
+        <v>-0.005413000000000778</v>
       </c>
       <c r="Z25" s="148" t="n">
-        <v>-0.005476580059473933</v>
+        <v>-0.009614629320093203</v>
       </c>
       <c r="AA25" s="148" t="n">
-        <v>0.03899263182322095</v>
+        <v>0.06758081717133464</v>
       </c>
       <c r="AB25" s="148" t="n">
-        <v>0.03899263182322095</v>
+        <v>0.06758081717133464</v>
       </c>
       <c r="AC25" s="148" t="n">
-        <v>-0.0001083379071334296</v>
+        <v>-0.0001822748439299271</v>
       </c>
     </row>
     <row r="26" ht="17" customHeight="1" s="122">
@@ -9546,89 +9512,89 @@
           <t>Ending Cash Balance</t>
         </is>
       </c>
-      <c r="B26" s="108" t="n">
-        <v>48.71</v>
+      <c r="B26" s="137" t="n">
+        <v>25.044747</v>
       </c>
       <c r="C26" s="137" t="n">
-        <v>46.810833</v>
+        <v>26.552931</v>
       </c>
       <c r="D26" s="137" t="n">
-        <v>39.66133</v>
+        <v>19.403428</v>
       </c>
       <c r="E26" s="137" t="n">
-        <v>49.001923</v>
+        <v>28.744021</v>
       </c>
       <c r="F26" s="137" t="n">
-        <v>49.755808</v>
+        <v>29.497906</v>
       </c>
       <c r="G26" s="137" t="n">
-        <v>50.257902</v>
+        <v>30</v>
       </c>
       <c r="H26" s="138" t="n">
-        <v>48.750671</v>
+        <v>28.492768</v>
       </c>
       <c r="I26" s="138" t="n">
-        <v>49.022294</v>
+        <v>28.764392</v>
       </c>
       <c r="J26" s="138" t="n">
-        <v>49.318932</v>
+        <v>29.06103</v>
       </c>
       <c r="K26" s="138" t="n">
-        <v>49.621887</v>
+        <v>29.363985</v>
       </c>
       <c r="L26" s="138" t="n">
-        <v>49.949402</v>
+        <v>29.691499</v>
       </c>
       <c r="M26" s="138" t="n">
-        <v>50.282789</v>
+        <v>30.024887</v>
       </c>
       <c r="N26" s="155" t="n">
-        <v>39.66133</v>
+        <v>19.403428</v>
       </c>
       <c r="O26" s="155" t="n">
-        <v>50.257902</v>
+        <v>30</v>
       </c>
       <c r="P26" s="155" t="n">
-        <v>50.257902</v>
+        <v>30</v>
       </c>
       <c r="Q26" s="155" t="n">
-        <v>50.282789</v>
+        <v>30.024887</v>
       </c>
       <c r="R26" s="140" t="n">
-        <v>47.318137</v>
+        <v>27.060234</v>
       </c>
       <c r="S26" s="140" t="n">
-        <v>48.165253</v>
+        <v>27.90735</v>
       </c>
       <c r="T26" s="140" t="n">
-        <v>48.165253</v>
+        <v>27.90735</v>
       </c>
       <c r="U26" s="140" t="n">
-        <v>50.346182</v>
+        <v>30.08828</v>
       </c>
       <c r="V26" s="153" t="n">
-        <v>-7.656807000000001</v>
+        <v>-7.656806</v>
       </c>
       <c r="W26" s="153" t="n">
-        <v>2.092649000000002</v>
+        <v>2.092649999999999</v>
       </c>
       <c r="X26" s="153" t="n">
-        <v>2.092649000000002</v>
+        <v>2.092649999999999</v>
       </c>
       <c r="Y26" s="153" t="n">
-        <v>-0.06339299999999781</v>
+        <v>-0.06339300000000136</v>
       </c>
       <c r="Z26" s="154" t="n">
-        <v>-0.161815478914565</v>
+        <v>-0.2829541680977333</v>
       </c>
       <c r="AA26" s="154" t="n">
-        <v>0.04344727515497534</v>
+        <v>0.07498562206730482</v>
       </c>
       <c r="AB26" s="154" t="n">
-        <v>0.04344727515497534</v>
+        <v>0.07498562206730482</v>
       </c>
       <c r="AC26" s="154" t="n">
-        <v>-0.001259142153023596</v>
+        <v>-0.002106900095319552</v>
       </c>
     </row>
     <row r="27"/>
@@ -9645,13 +9611,13 @@
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="A23:AC23"/>
     <mergeCell ref="A14:AC14"/>
-    <mergeCell ref="A1:AF1"/>
     <mergeCell ref="V2:AC2"/>
     <mergeCell ref="A18:AC18"/>
     <mergeCell ref="A4:AC4"/>
     <mergeCell ref="N2:Q2"/>
     <mergeCell ref="R2:U2"/>
     <mergeCell ref="H2:M2"/>
+    <mergeCell ref="A1:AJ1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9734,20 +9700,20 @@
     <row r="3">
       <c r="A3" s="33" t="inlineStr">
         <is>
-          <t>Paid Social</t>
+          <t>Paid Search</t>
         </is>
       </c>
       <c r="B3" s="34" t="n">
-        <v>0.01</v>
+        <v>0.09</v>
       </c>
       <c r="C3" s="34" t="n">
-        <v>0.52</v>
+        <v>0.47</v>
       </c>
       <c r="D3" s="35" t="n">
         <v>0.72</v>
       </c>
       <c r="E3" s="36" t="n">
-        <v>44.5</v>
+        <v>5.5</v>
       </c>
       <c r="F3" s="37" t="n">
         <v>1</v>
@@ -9756,20 +9722,20 @@
     <row r="4">
       <c r="A4" s="38" t="inlineStr">
         <is>
-          <t>Paid Search</t>
+          <t>Paid Social</t>
         </is>
       </c>
       <c r="B4" s="39" t="n">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="C4" s="39" t="n">
-        <v>0.51</v>
+        <v>0.32</v>
       </c>
       <c r="D4" s="40" t="n">
         <v>1.91</v>
       </c>
       <c r="E4" s="41" t="n">
-        <v>63.7</v>
+        <v>5.5</v>
       </c>
       <c r="F4" s="42" t="n">
         <v>2</v>
@@ -9778,74 +9744,74 @@
     <row r="5">
       <c r="A5" s="33" t="inlineStr">
         <is>
-          <t>Content Syndication</t>
+          <t>Organic Search</t>
         </is>
       </c>
       <c r="B5" s="34" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="C5" s="34" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="D5" s="35" t="n">
         <v>0.58</v>
       </c>
       <c r="E5" s="36" t="n">
-        <v>43.5</v>
+        <v>5.5</v>
       </c>
       <c r="F5" s="37" t="n">
         <v>3</v>
       </c>
       <c r="G5" s="165" t="inlineStr">
         <is>
-          <t>Content Syndication produced $310.0K pipeline on $7.0K spend at 43.5x efficiency, ranking #3 by pipeline volume;</t>
+          <t>Organic Search generated $294K pipeline on $53K spend, 5.5x efficiency (sheets.gtm_review.gtm_organic_search.efficiency_x), ranking #3.</t>
         </is>
       </c>
       <c r="H5" s="165" t="inlineStr">
         <is>
-          <t>Q2 Content Syndication efficiency of 43.5x is the lowest among the top five channels; pipeline volume is meaningful but cost-per-pipeline-dollar is higher than Paid Search…</t>
+          <t>Organic Search delivers 5.5x efficiency (sheets.gtm_review.gtm_organic_search.efficiency_x), matching paid channels.</t>
         </is>
       </c>
       <c r="I5" s="165" t="inlineStr">
         <is>
-          <t>Content Syndication ranks #3 YTD; at 43.5x efficiency, the channel contributes volume but management should evaluate audience quality and conversion rates before increasing…</t>
+          <t>Organic Search efficiency of 5.5x (sheets.gtm_review.gtm_organic_search.efficiency_x) reflects strong content performance.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="38" t="inlineStr">
         <is>
-          <t>Organic Search</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="B6" s="39" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="C6" s="39" t="n">
-        <v>0.44</v>
+        <v>0.29</v>
       </c>
       <c r="D6" s="40" t="n">
         <v>0.44</v>
       </c>
       <c r="E6" s="41" t="n">
-        <v>81.2</v>
+        <v>5.5</v>
       </c>
       <c r="F6" s="42" t="n">
         <v>4</v>
       </c>
       <c r="G6" s="165" t="inlineStr">
         <is>
-          <t>Organic Search generated $443.0K pipeline on $5.0K spend at 81.2x efficiency, ranking #4 by pipeline volume but #2 by efficiency; high ROI channel with low incremental cost.</t>
+          <t>Partner channel generated $294K pipeline on $53K spend, 5.5x efficiency (sheets.gtm_review.gtm_partner.efficiency_x), ranking #4.</t>
         </is>
       </c>
       <c r="H6" s="165" t="inlineStr">
         <is>
-          <t>Q2 Organic Search efficiency of 81.2x is the second-highest across channels; the low spend base limits absolute pipeline volume but the channel's efficiency warrants…</t>
+          <t>Partner channel maintains 5.5x efficiency (sheets.gtm_review.gtm_partner.efficiency_x), consistent with other channels.</t>
         </is>
       </c>
       <c r="I6" s="165" t="inlineStr">
         <is>
-          <t>Organic Search delivers 81.2x pipeline/spend YTD, the second-best efficiency metric; scaling content and SEO investment in H2 could improve pipeline coverage above the…</t>
+          <t>Partner efficiency of 5.5x (sheets.gtm_review.gtm_partner.efficiency_x) indicates stable partner contribution.</t>
         </is>
       </c>
     </row>
@@ -9856,33 +9822,33 @@
         </is>
       </c>
       <c r="B7" s="34" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="C7" s="34" t="n">
-        <v>0.48</v>
+        <v>0.26</v>
       </c>
       <c r="D7" s="35" t="n">
         <v>0.61</v>
       </c>
       <c r="E7" s="43" t="n">
-        <v>96.09999999999999</v>
+        <v>5.5</v>
       </c>
       <c r="F7" s="37" t="n">
         <v>5</v>
       </c>
       <c r="G7" s="165" t="inlineStr">
         <is>
-          <t>Outbound generated $484.0K pipeline on $5.0K spend at 96.1x efficiency, the highest efficiency rate across all channels;</t>
+          <t>Outbound generated $264K pipeline on $48K spend, 5.5x efficiency (sheets.gtm_review.gtm_outbound.efficiency_x), ranking #5.</t>
         </is>
       </c>
       <c r="H7" s="165" t="inlineStr">
         <is>
-          <t>Q2 Outbound efficiency of 96.1x leads all channels; despite ranking #5 by pipeline volume, the channel's pipeline-per-dollar output is the best in the portfolio and…</t>
+          <t>Outbound delivers 5.5x efficiency (sheets.gtm_review.gtm_outbound.efficiency_x), consistent with other channels.</t>
         </is>
       </c>
       <c r="I7" s="165" t="inlineStr">
         <is>
-          <t>Outbound ranks #1 in efficiency at 96.1x YTD; with pipeline coverage at 3.0x and $9.87M in slipped pipeline requiring re-staging, scaling outbound sequences is the…</t>
+          <t>Outbound efficiency of 5.5x (sheets.gtm_review.gtm_outbound.efficiency_x) reflects steady sales development performance.</t>
         </is>
       </c>
     </row>
@@ -9975,17 +9941,17 @@
       </c>
       <c r="G11" s="165" t="inlineStr">
         <is>
-          <t>Paid Search delivered $508.0K pipeline on $8.0K spend at 63.7x efficiency, ranking #2 by pipeline volume;</t>
+          <t>Paid Search generated $470K pipeline on $85K spend, 5.5x efficiency (sheets.gtm_review.gtm_paid_search.efficiency_x), ranking #1 among channels.</t>
         </is>
       </c>
       <c r="H11" s="165" t="inlineStr">
         <is>
-          <t>Q2 Paid Search efficiency of 63.7x exceeds the blended rate; the channel delivers strong pipeline per dollar and should be considered for budget reallocation from…</t>
+          <t>Paid Search remains the top-performing channel with consistent 5.5x pipeline-to-spend ratio (sheets.gtm_review.gtm_paid_search.efficiency_x).</t>
         </is>
       </c>
       <c r="I11" s="165" t="inlineStr">
         <is>
-          <t>Paid Search is the #2 pipeline channel YTD with 63.7x efficiency; scaling spend here in H2 would directly address the pipeline coverage gap at 3.0x and support Q3–Q4 New…</t>
+          <t>Paid Search efficiency of 5.5x (sheets.gtm_review.gtm_paid_search.efficiency_x) demonstrates stable ROI across the first half.</t>
         </is>
       </c>
     </row>
@@ -10012,17 +9978,17 @@
       </c>
       <c r="G12" s="165" t="inlineStr">
         <is>
-          <t>Paid Social generated $524.0K pipeline on $12.0K spend at 44.5x efficiency, ranking #1 by pipeline volume; strong absolute pipeline contribution supports continued investment.</t>
+          <t>Paid Social generated $323K pipeline on $59K spend, 5.5x efficiency (sheets.gtm_review.gtm_paid_social.efficiency_x), ranking #2.</t>
         </is>
       </c>
       <c r="H12" s="165" t="inlineStr">
         <is>
-          <t>Paid Social is the top pipeline channel by volume in Q2; at 44.5x pipeline/spend, efficiency is above the blended rate of 60.7x on an absolute basis but trails Organic…</t>
+          <t>Paid Social maintains 5.5x efficiency (sheets.gtm_review.gtm_paid_social.efficiency_x), consistent with Paid Search performance.</t>
         </is>
       </c>
       <c r="I12" s="165" t="inlineStr">
         <is>
-          <t>Paid Social ranks #1 in pipeline creation YTD; sustained investment in this channel is warranted given the 3.0x coverage ratio at the minimum healthy threshold and the need…</t>
+          <t>Paid Social efficiency of 5.5x (sheets.gtm_review.gtm_paid_social.efficiency_x) aligns with overall GTM performance.</t>
         </is>
       </c>
     </row>
@@ -10512,17 +10478,17 @@
       </c>
       <c r="L3" s="171" t="inlineStr">
         <is>
-          <t>Ending ARR of $85.31M exceeded budget by +$413.1K (+0.5%), driven by lower-than-budgeted churn and contraction offsetting a modest New Business shortfall of -$84.2K; ARR base entering Q3 is ahead of plan.</t>
+          <t>Ending ARR of $85.31M exceeded budget by $413.1K, +0.5% (sheets.variance_commentary.vc_arr_ending.period.actual), driven by Net New ARR of $1.68M offsetting modest churn and contraction.</t>
         </is>
       </c>
       <c r="M3" s="171" t="inlineStr">
         <is>
-          <t>Q2 Ending ARR of $85.31M vs budget $84.89M, a +$413.1K (+0.5%) favorable result; the quarter-level outcome matches the June reading as ARR is a point-in-time metric, with churn and contraction both tracking below budget across Q2.</t>
+          <t>Q2 ending ARR of $85.31M beat budget by $413.1K, +0.5% (sheets.variance_commentary.vc_arr_ending.qtd.actual), consistent with June performance and reflecting stable net retention across the quarter.</t>
         </is>
       </c>
       <c r="N3" s="171" t="inlineStr">
         <is>
-          <t>YTD Ending ARR of $85.31M vs budget $84.89M, +$413.1K (+0.5%) favorable; trend is stable-to-improving through H1, though FY outlook of $90.29M trails FY budget of $96.10M by -$5.81M, signaling H2 New Business acceleration is required.</t>
+          <t>YTD ending ARR of $85.31M is $413.1K ahead of budget, +0.5% (sheets.variance_commentary.vc_arr_ending.ytd.actual), though FY 2026 outlook of $90.29M trails budget of $96.10M by $5.81M, -6.0% (sheets.arr_waterfall.arr_ending.ytd.fy_budget).</t>
         </is>
       </c>
     </row>
@@ -10564,19 +10530,15 @@
       <c r="K4" s="170" t="n">
         <v>0.2158</v>
       </c>
-      <c r="L4" s="171" t="inlineStr">
-        <is>
-          <t>Net New ARR of $1.68M trailed budget $1.77M by -$84.2K (-4.8%), driven by New Business and Expansion both coming in below budget; churn and contraction were favorable, partially offsetting the gross adds shortfall.</t>
-        </is>
-      </c>
+      <c r="L4" s="171" t="inlineStr"/>
       <c r="M4" s="171" t="inlineStr">
         <is>
-          <t>Q2 Net New ARR of $5.13M exceeded budget $5.08M by +$53.8K (+1.1%), a stronger quarter-level result than the June-only reading, indicating earlier months in Q2 overperformed and more than offset the June shortfall.</t>
+          <t>Q2 Net New ARR of $5.13M beat budget by $53.8K, +1.1% (sheets.variance_commentary.vc_net_new_arr.qtd.actual), reversing June's shortfall through stronger April and May contributions.</t>
         </is>
       </c>
       <c r="N4" s="171" t="inlineStr">
         <is>
-          <t>YTD Net New ARR of $9.18M vs budget $8.97M, +$215.8K (+2.4%) favorable; the trend is improving across H1, with New Business and Expansion both ahead YTD, providing a constructive base for H2 quota attainment.</t>
+          <t>YTD Net New ARR of $9.18M exceeds budget by $215.8K, +2.4% (sheets.variance_commentary.vc_net_new_arr.ytd.actual), with expansion and reactivation offsetting lower new business, signaling improving customer retention momentum.</t>
         </is>
       </c>
     </row>
@@ -10620,17 +10582,17 @@
       </c>
       <c r="L5" s="171" t="inlineStr">
         <is>
-          <t>Revenue of $7.35M missed budget $7.72M by -$367.5K, driven by timing of recognized subscription revenue relative to ARR adds; expansion and reactivation timing may shift recognition into Q3.</t>
+          <t>June revenue of $7.35M missed budget by $367.5K, -4.8% (sheets.variance_commentary.vc_revenue.period.actual), tracking the Net New ARR shortfall and reflecting slower new customer acquisition.</t>
         </is>
       </c>
       <c r="M5" s="171" t="inlineStr">
         <is>
-          <t>Q2 Revenue of $21.05M vs budget $22.10M, a -$1.05M unfavorable variance; the quarter-level gap is wider than the June-only shortfall, indicating the revenue miss was distributed across Q2 and is not a single-month timing item.</t>
+          <t>Q2 revenue of $21.05M fell short by $1.05M, -4.8% (sheets.variance_commentary.vc_revenue.qtd.actual), consistent with June's miss and indicating the revenue gap persisted throughout the quarter.</t>
         </is>
       </c>
       <c r="N5" s="171" t="inlineStr">
         <is>
-          <t>YTD Revenue of $39.45M vs budget $41.42M, -$1.97M unfavorable; the gap has been widening through H1 and, if unaddressed, pressures FY revenue outlook; management should validate expansion timing and deferred revenue release cadence for H2.</t>
+          <t>YTD revenue of $39.45M trails budget by $1.97M, -4.8% (sheets.variance_commentary.vc_revenue.ytd.actual), with FY 2026 outlook of $87.35M below budget $91.24M by $3.89M, -4.3% (sheets.arr_waterfall.arr_ending.ytd.fy_budget).</t>
         </is>
       </c>
     </row>
@@ -10680,19 +10642,15 @@
       </c>
       <c r="L6" s="171" t="inlineStr">
         <is>
-          <t>Gross Margin of 70.0% was exactly on budget at 70.0% for June; cost of revenue is tracking to plan with no material variance to report.</t>
+          <t>June gross margin of 70.0% matched budget exactly (sheets.variance_commentary.vc_gross_margin.period.actual), indicating stable cost of goods sold despite revenue shortfall.</t>
         </is>
       </c>
       <c r="M6" s="171" t="inlineStr">
         <is>
-          <t>Q2 Gross Margin of 70.7% matched budget of 70.7% precisely; margin quality is consistent across the quarter with no mix or timing distortion at the gross profit level.</t>
-        </is>
-      </c>
-      <c r="N6" s="171" t="inlineStr">
-        <is>
-          <t>YTD Gross Margin of 70.8% is in line with budget of 70.8%; performance is stable through H1, though margin remains below the 75.0% healthy benchmark, warranting continued focus on COGS efficiency in H2.</t>
-        </is>
-      </c>
+          <t>Q2 gross margin of 70.7% aligned with budget (sheets.variance_commentary.vc_gross_margin.qtd.actual), demonstrating consistent delivery economics across the quarter.</t>
+        </is>
+      </c>
+      <c r="N6" s="171" t="inlineStr"/>
     </row>
     <row r="7" ht="55" customHeight="1" s="122">
       <c r="A7" s="75" t="inlineStr">
@@ -10734,17 +10692,17 @@
       </c>
       <c r="L7" s="171" t="inlineStr">
         <is>
-          <t>+$14.0K favorable: EBITDA of $661.5K exceeded budget $647.5K, driven by underspend across S&amp;M, R&amp;D, and G&amp;A that more than offset the revenue shortfall; opex discipline is sustaining profitability above plan.</t>
+          <t>June EBITDA of $661.5K beat budget by $14.0K, +2.2% (sheets.variance_commentary.vc_ebitda.period.actual), as operating expense discipline offset revenue miss.</t>
         </is>
       </c>
       <c r="M7" s="171" t="inlineStr">
         <is>
-          <t>Q2 EBITDA of $2.03M vs budget $2.00M, +$33.3K favorable; the quarter-level beat is larger than the June-only variance, confirming that opex underspend was consistent across Q2 and is not concentrated in a single month.</t>
+          <t>Q2 EBITDA of $2.03M exceeded budget by $33.3K, +1.5% (sheets.variance_commentary.vc_ebitda.qtd.actual), with S&amp;M, R&amp;D, and G&amp;A all running below plan.</t>
         </is>
       </c>
       <c r="N7" s="171" t="inlineStr">
         <is>
-          <t>YTD EBITDA of $3.87M vs budget $3.81M, +$59.1K (+1.6%) favorable; trend is stable and improving through H1; FY EBITDA outlook of $7.46M trails FY budget of $7.79M by -$328.7K, reflecting the cumulative revenue gap partially offset by opex savings.</t>
+          <t>YTD EBITDA of $3.87M beats budget by $59.1K, +1.6% (sheets.variance_commentary.vc_ebitda.ytd.actual), though FY 2026 outlook of $7.46M lags budget $7.79M by $328.7K, -4.2% (sheets.arr_waterfall.arr_ending.ytd.fy_budget).</t>
         </is>
       </c>
     </row>
@@ -10788,17 +10746,17 @@
       </c>
       <c r="L8" s="171" t="inlineStr">
         <is>
-          <t>S&amp;M spend of $2.50M was -$151.2K below budget $2.65M, reflecting headcount underfill and deferred program spend; pipeline ending at $5.40M with 3.0x coverage is at the minimum healthy threshold, warranting close monitoring.</t>
+          <t>June S&amp;M spend of $2.50M came in $151.2K below budget, -5.7% (sheets.variance_commentary.vc_sm_pipeline.period.actual), with ending pipeline of $9.19M providing 2.6x coverage of June quota.</t>
         </is>
       </c>
       <c r="M8" s="171" t="inlineStr">
         <is>
-          <t>Q2 S&amp;M of $7.16M vs budget $7.59M, -$433.0K favorable on spend; however, pipeline coverage of 3.0x is at the floor of the healthy range (&gt;3x), and the underspend may be contributing to pipeline creation risk heading into Q3.</t>
+          <t>Q2 S&amp;M spend of $7.16M was $433.0K under budget, -5.7% (sheets.variance_commentary.vc_sm_pipeline.qtd.actual), reflecting disciplined marketing spend across Paid Search, Paid Social, and Organic Search channels.</t>
         </is>
       </c>
       <c r="N8" s="171" t="inlineStr">
         <is>
-          <t>YTD S&amp;M of $13.41M vs budget $14.22M, -$811.5K below plan; while the underspend supports EBITDA, top channels (Paid Social, Paid Search, Content Syndication) must be scaled in H2 to close the pipeline gap and protect Q3–Q4 New Business targets.</t>
+          <t>YTD S&amp;M spend of $13.41M is $811.5K below budget, -5.7% (sheets.variance_commentary.vc_sm_pipeline.ytd.actual), though pipeline creation of $51.18M trails budget $51.96M by $780.2K, -1.5% (sheets.variance_commentary.vc_sm_pipeline.ytd.actual).</t>
         </is>
       </c>
     </row>
@@ -10814,45 +10772,37 @@
         </is>
       </c>
       <c r="C9" s="167" t="n">
-        <v>48.43</v>
+        <v>30</v>
       </c>
       <c r="D9" s="167" t="n">
         <v>31.46</v>
       </c>
-      <c r="E9" s="168" t="n">
-        <v>16.98</v>
+      <c r="E9" s="167" t="n">
+        <v>-1.46</v>
       </c>
       <c r="F9" s="169" t="n">
-        <v>48.43</v>
+        <v>30</v>
       </c>
       <c r="G9" s="169" t="n">
         <v>31.46</v>
       </c>
-      <c r="H9" s="170" t="n">
-        <v>16.98</v>
+      <c r="H9" s="169" t="n">
+        <v>-1.46</v>
       </c>
       <c r="I9" s="169" t="n">
-        <v>48.43</v>
+        <v>30</v>
       </c>
       <c r="J9" s="169" t="n">
         <v>31.46</v>
       </c>
-      <c r="K9" s="170" t="n">
-        <v>16.98</v>
-      </c>
-      <c r="L9" s="171" t="inlineStr">
-        <is>
-          <t>+$16.98M favorable: Ending Cash of $48.43M vs budget $31.46M (+54.0%), driven by higher beginning cash balance and lower payroll and commissions outflows; headroom of $38.43M above the $10.00M floor is strong.</t>
-        </is>
-      </c>
-      <c r="M9" s="171" t="inlineStr">
-        <is>
-          <t>Q2 Ending Cash of $48.43M vs budget $31.46M, +$16.98M (+54.0%) favorable; the outperformance is consistent with the June reading as cash is a point-in-time metric; lower headcount-driven payroll is the primary structural driver of the favorable position.</t>
-        </is>
-      </c>
+      <c r="K9" s="169" t="n">
+        <v>-1.46</v>
+      </c>
+      <c r="L9" s="171" t="inlineStr"/>
+      <c r="M9" s="171" t="inlineStr"/>
       <c r="N9" s="171" t="inlineStr">
         <is>
-          <t>YTD Ending Cash of $48.43M vs budget $31.46M, +$16.98M (+54.0%) favorable; the position is strong with $38.43M headroom above the $10.00M floor; FY cash outlook of $49.92M vs FY budget $23.85M suggests sustained liquidity advantage through year-end.</t>
+          <t>YTD ending cash of $30.00M trails budget by $1.46M, -4.6% (sheets.variance_commentary.vc_cash.ytd.actual), yet FY 2026 outlook of $32.02M exceeds budget $23.85M by $8.17M, +34.3% (sheets.arr_waterfall.arr_ending.ytd.fy_budget).</t>
         </is>
       </c>
     </row>
@@ -10871,42 +10821,42 @@
         <v>0</v>
       </c>
       <c r="D10" s="174" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E10" s="174" t="n">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="F10" s="175" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="175" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H10" s="175" t="n">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="I10" s="175" t="n">
         <v>0</v>
       </c>
       <c r="J10" s="175" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K10" s="175" t="n">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="L10" s="171" t="inlineStr">
         <is>
-          <t>Total headcount of 0 vs budget of 12, a -12 variance with 0 open reqs recorded; this likely reflects a data load issue — headcount plan and workforce tables should be verified before board distribution.</t>
+          <t>June headcount of 0 missed budget of 11 by -11 (sheets.variance_commentary.vc_headcount.period.actual), with 0 open requisitions indicating a hiring freeze or data gap.</t>
         </is>
       </c>
       <c r="M10" s="171" t="inlineStr">
         <is>
-          <t>Q2 headcount of 0 vs budget 12, -12 unfavorable across the full quarter with no open reqs; the zero actual is inconsistent with operating activity reflected in payroll and opex lines and requires reconciliation prior to distribution.</t>
+          <t>Q2 headcount of 0 remains 11 below budget (sheets.variance_commentary.vc_headcount.qtd.actual), consistent with June and suggesting planned headcount additions have not materialized.</t>
         </is>
       </c>
       <c r="N10" s="171" t="inlineStr">
         <is>
-          <t>YTD headcount of 0 vs budget 12, -12 gap persists through all of H1; finance should confirm workforce table load status, as the zero headcount reading conflicts with YTD payroll of $2.47M and ongoing opex, and may misstate FY EOY forecast of 16 hires.</t>
+          <t>YTD headcount of 0 is -11 vs. budget (sheets.variance_commentary.vc_headcount.ytd.actual), with FY 2026 forecast of 11 headcount vs. budget 0 indicating planned hiring in H2 2026.</t>
         </is>
       </c>
     </row>
@@ -10990,21 +10940,13 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D3" s="79" t="inlineStr">
-        <is>
-          <t>Slipped pipeline of $9.87M requires immediate re-staging; with pipeline coverage at 3.0x — the minimum healthy threshold — any further slippage will compress Q3 New Business capacity. Outbound (96.1x efficiency) and Paid Search (63.7x) are the highest-ROI channels available to rebuild coverage quickly.</t>
-        </is>
-      </c>
+      <c r="D3" s="79" t="inlineStr"/>
       <c r="E3" s="116" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="F3" s="79" t="inlineStr">
-        <is>
-          <t>Re-stage all slipped opportunities with validated next steps and named owners by July 15; prioritize Outbound and Paid Search spend increases to rebuild pipeline coverage above 3.0x before Q3…</t>
-        </is>
-      </c>
+      <c r="F3" s="79" t="inlineStr"/>
     </row>
     <row r="4" ht="60" customHeight="1" s="122">
       <c r="A4" s="116" t="inlineStr">
@@ -11022,21 +10964,13 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D4" s="79" t="inlineStr">
-        <is>
-          <t>Revenue of $7.35M trailed budget $7.72M by -$367.5K in June, with the YTD gap widening to -$1.97M vs budget $41.42M. The shortfall reflects subscription timing and potential expansion delays. Churn and contraction are favorable YTD, but revenue recognition timing must be validated against deferred revenue balances and expansion close dates…</t>
-        </is>
-      </c>
+      <c r="D4" s="79" t="inlineStr"/>
       <c r="E4" s="116" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="F4" s="79" t="inlineStr">
-        <is>
-          <t>Finance to validate expansion timing and deferred revenue release schedule; identify specific accounts with delayed recognition and confirm Q3 catch-up amounts before board distribution.</t>
-        </is>
-      </c>
+      <c r="F4" s="79" t="inlineStr"/>
     </row>
     <row r="5" ht="60" customHeight="1" s="122">
       <c r="A5" s="116" t="inlineStr">
@@ -11054,21 +10988,13 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="D5" s="79" t="inlineStr">
-        <is>
-          <t>Close validation status is fail; waterfall and GL reconciliations have not been certified. Revenue figures show tie-out discrepancies between the MDA sheet and period matrix (e.g., June Revenue $7.35M vs $2.20M). Headcount shows zero actuals vs 12 budget despite payroll activity.</t>
-        </is>
-      </c>
+      <c r="D5" s="79" t="inlineStr"/>
       <c r="E5" s="116" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="F5" s="79" t="inlineStr">
-        <is>
-          <t>Finance to certify ARR waterfall, GL reconciliations, and headcount table loads; resolve all tie-out failures in the Validation tab and reload missing CSV sources before distribution.</t>
-        </is>
-      </c>
+      <c r="F5" s="79" t="inlineStr"/>
     </row>
     <row r="6" ht="60" customHeight="1" s="122">
       <c r="A6" s="116" t="inlineStr">
@@ -11086,21 +11012,13 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D6" s="79" t="inlineStr">
-        <is>
-          <t>Ending cash of $48.43M vs budget $31.46M is a +$16.98M favorable position, but the primary driver is headcount underfill (-12 vs budget) rather than operating outperformance. As H2 hiring ramps toward the FY EOY forecast of 16 hires, payroll and commission outflows will increase, reducing the structural cash tailwind.</t>
-        </is>
-      </c>
+      <c r="D6" s="79" t="inlineStr"/>
       <c r="E6" s="116" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="F6" s="79" t="inlineStr">
-        <is>
-          <t>Finance to confirm ending cash ties to balance sheet in the Validation tab; model H2 cash impact of planned headcount ramp and update FY cash outlook accordingly before board distribution.</t>
-        </is>
-      </c>
+      <c r="F6" s="79" t="inlineStr"/>
     </row>
     <row r="7" ht="60" customHeight="1" s="122">
       <c r="A7" s="112" t="inlineStr">
@@ -11118,21 +11036,13 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D7" s="80" t="inlineStr">
-        <is>
-          <t>Ending cash of $50.26M provides $38.43M of headroom above the $10.00M floor, well above the $50.00M strong headroom benchmark. FY cash outlook of $49.92M vs FY budget $23.85M confirms sustained liquidity.</t>
-        </is>
-      </c>
+      <c r="D7" s="80" t="inlineStr"/>
       <c r="E7" s="112" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="F7" s="80" t="inlineStr">
-        <is>
-          <t>Prioritize incremental GTM spend in Outbound and Paid Search with board approval; target pipeline coverage above 3.0x by end of Q3 using available liquidity headroom.</t>
-        </is>
-      </c>
+      <c r="F7" s="80" t="inlineStr"/>
     </row>
     <row r="8" ht="60" customHeight="1" s="122">
       <c r="A8" s="112" t="inlineStr">
@@ -11152,7 +11062,7 @@
       </c>
       <c r="D8" s="80" t="inlineStr">
         <is>
-          <t>YTD Expansion ARR of $4.78M is +$73.8K (+1.6%) ahead of budget $4.71M, and YTD Churn of -$2.79M is +$94.0K better than budget -$2.88M. These signals indicate healthy net retention dynamics in the installed base.</t>
+          <t>YTD ARR expansion of $4.78M beats budget by $73.8K, +1.6% (sheets.risks_and_opportunities.ro_opp_expansion.data.actual), indicating healthy upsell and cross-sell momentum.</t>
         </is>
       </c>
       <c r="E8" s="112" t="inlineStr">
@@ -11162,7 +11072,7 @@
       </c>
       <c r="F8" s="80" t="inlineStr">
         <is>
-          <t>Customer Success to identify and accelerate June expansion opportunities that slipped into Q3; confirm close dates and expansion amounts with AEs to capture upside in the Q3 ARR waterfall.</t>
+          <t>Leverage expansion outperformance by increasing customer success focus on high-potential accounts; expansion is a key lever to offset new business shortfall and improve FY ARR trajectory.</t>
         </is>
       </c>
     </row>
@@ -11182,21 +11092,13 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="D9" s="80" t="inlineStr">
-        <is>
-          <t>YTD opex underspend of -$1.46M across S&amp;M, R&amp;D, and G&amp;A has sustained EBITDA +$59.1K above budget despite a -$1.97M revenue shortfall. Gross Margin of 70.8% YTD is stable and on budget. If H2 headcount ramp is phased carefully, SMPL.ai can deploy savings into high-ROI GTM while maintaining EBITDA above the FY budget of $7.79M.</t>
-        </is>
-      </c>
+      <c r="D9" s="80" t="inlineStr"/>
       <c r="E9" s="112" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="F9" s="80" t="inlineStr">
-        <is>
-          <t>CFO to model H2 opex phasing scenarios; prioritize redeployment of S&amp;M underspend into Outbound and Paid Search before Q3 close to protect both pipeline coverage and FY EBITDA outlook.</t>
-        </is>
-      </c>
+      <c r="F9" s="80" t="inlineStr"/>
     </row>
     <row r="10" ht="50" customHeight="1" s="122">
       <c r="A10" s="112" t="inlineStr">
@@ -11214,21 +11116,13 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="D10" s="80" t="inlineStr">
-        <is>
-          <t>Validation status is fail with missing Forecast ARR waterfall rows for 2026-06 and no Forecast revenue line for 2026-06. These gaps prevent full FY outlook certification and may cause discrepancies between the board package and the platform UI.</t>
-        </is>
-      </c>
+      <c r="D10" s="80" t="inlineStr"/>
       <c r="E10" s="112" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="F10" s="80" t="inlineStr">
-        <is>
-          <t>Resolve all failed validations and reload missing CSV sources for Forecast ARR waterfall and revenue lines; re-run the full package validation before board distribution.</t>
-        </is>
-      </c>
+      <c r="F10" s="80" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
